--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487813_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487813_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1065</v>
+        <v>6.0082</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3654</v>
+        <v>4.4726</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7411</v>
+        <v>1.5356</v>
       </c>
       <c r="G2" t="n">
         <v>4.3265</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.7681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3477</v>
+        <v>0.4548</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5187</v>
+        <v>0.3132</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1675</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5519</v>
+        <v>4.8124</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7533</v>
+        <v>2.9257</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7986</v>
+        <v>1.8867</v>
       </c>
       <c r="G3" t="n">
         <v>1.8075</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1494</v>
+        <v>0.1111</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3601</v>
+        <v>0.5325</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5095</v>
+        <v>-0.4214</v>
       </c>
       <c r="V3" t="n">
         <v>1.6452</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4538</v>
+        <v>4.3301</v>
       </c>
       <c r="E4" t="n">
-        <v>2.13</v>
+        <v>2.5215</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3238</v>
+        <v>1.8086</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2809</v>
+        <v>-0.332</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2026</v>
+        <v>-0.9337</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9217</v>
+        <v>0.6017</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7706</v>
+        <v>1.1786</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7616000000000001</v>
+        <v>0.2258</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.9527</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4897</v>
+        <v>-1.5106</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4411</v>
+        <v>-1.1596</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9307</v>
+        <v>-0.351</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8731</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-4.3705</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0812</v>
+        <v>3.7461</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6317</v>
+        <v>0.0326</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7112</v>
+        <v>0.2296</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0795</v>
+        <v>-0.197</v>
       </c>
       <c r="V4" t="n">
-        <v>0.23</v>
+        <v>5.2539</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3975</v>
+        <v>5.4838</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3331</v>
+        <v>4.1419</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1709</v>
+        <v>0.5792</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5039</v>
+        <v>3.5627</v>
       </c>
       <c r="G5" t="n">
         <v>1.2849</v>
@@ -844,13 +844,13 @@
         <v>2.9137</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9081</v>
+        <v>-0.0993</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5624</v>
+        <v>0.1877</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3457</v>
+        <v>-0.287</v>
       </c>
       <c r="V5" t="n">
         <v>1.2914</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1793</v>
+        <v>2.4116</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6643</v>
+        <v>1.0585</v>
       </c>
       <c r="F6" t="n">
-        <v>1.515</v>
+        <v>1.3531</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.332</v>
+        <v>-0.2809</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9337</v>
+        <v>-1.2026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6017</v>
+        <v>0.9217</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1786</v>
+        <v>-0.7706</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2258</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9527</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5106</v>
+        <v>0.4897</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1596</v>
+        <v>-0.4411</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.351</v>
+        <v>0.9307</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.3705</v>
+        <v>-0.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7461</v>
+        <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1182</v>
+        <v>0.5895</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6277</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4906</v>
+        <v>-0.0502</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2539</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>5.4838</v>
+        <v>1.3975</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7557</v>
+        <v>0.4297</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9645</v>
+        <v>0.223</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2088</v>
+        <v>0.2067</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1958</v>
+        <v>-3.0459</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0767</v>
+        <v>-0.0195</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8809</v>
+        <v>-3.0265</v>
       </c>
       <c r="J7" t="n">
-        <v>2.592</v>
+        <v>-1.0618</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5137</v>
+        <v>1.0421</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0784</v>
+        <v>-2.1039</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3962</v>
+        <v>-1.9841</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4369</v>
+        <v>-1.0616</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9593</v>
+        <v>-0.9225</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S7" t="n">
-        <v>1.9168</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6212</v>
+        <v>0.2172</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2956</v>
+        <v>-0.3066</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.565</v>
+        <v>3.1488</v>
       </c>
       <c r="W7" t="n">
+        <v>3.1488</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3639</v>
+        <v>-0.2968</v>
       </c>
       <c r="E8" t="n">
-        <v>0.627</v>
+        <v>2.0001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9909</v>
+        <v>-2.2969</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0348</v>
+        <v>1.1958</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1449</v>
+        <v>2.0767</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8899</v>
+        <v>-0.8809</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0959</v>
+        <v>2.592</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0959</v>
+        <v>2.5137</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1308</v>
+        <v>-1.3962</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2409</v>
+        <v>-0.4369</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8899</v>
+        <v>-0.9593</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5898</v>
+        <v>0.8643</v>
       </c>
       <c r="T8" t="n">
-        <v>0.531</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0587</v>
+        <v>0.2075</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6983</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6995</v>
+        <v>0.3055</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0012</v>
+        <v>-0.9028</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0459</v>
+        <v>-1.0348</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0195</v>
+        <v>-0.1449</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0265</v>
+        <v>-0.8899</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0618</v>
+        <v>0.0959</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0421</v>
+        <v>0.0959</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1039</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9841</v>
+        <v>-1.1308</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0616</v>
+        <v>-0.2409</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9225</v>
+        <v>-0.8899</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4974</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2174</v>
+        <v>0.3564</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7053</v>
+        <v>0.2096</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5121</v>
+        <v>0.1468</v>
       </c>
       <c r="V9" t="n">
-        <v>3.1488</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.178</v>
+        <v>-1.6398</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1979</v>
+        <v>-1.4542</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0199</v>
+        <v>-0.1856</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3048</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6054</v>
+        <v>0.1437</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.2624</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0868</v>
+        <v>-0.1187</v>
       </c>
       <c r="V10" t="n">
         <v>0.3538</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8996</v>
+        <v>-5.4733</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3456</v>
+        <v>-3.0661</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.554</v>
+        <v>-2.4072</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0999</v>
@@ -1312,13 +1312,13 @@
         <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6322</v>
+        <v>-0.2058</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0562</v>
+        <v>0.2234</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.576</v>
+        <v>-0.4292</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7513</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4089</v>
+        <v>-6.969</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9918</v>
+        <v>-6.1409</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4172</v>
+        <v>-0.8282</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0668</v>
@@ -1390,13 +1390,13 @@
         <v>2.4974</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8847</v>
+        <v>0.3246</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4625</v>
+        <v>0.3134</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4222</v>
+        <v>0.0111</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5213</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.831600000000001</v>
+        <v>7.157699999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>3.098799999999999</v>
+        <v>3.424900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.732599999999999</v>
+        <v>3.7327</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5504</v>
       </c>
       <c r="H13" t="n">
-        <v>3.389100000000001</v>
+        <v>3.3891</v>
       </c>
       <c r="I13" t="n">
         <v>-6.9396</v>
       </c>
       <c r="J13" t="n">
-        <v>5.881099999999999</v>
+        <v>5.881099999999997</v>
       </c>
       <c r="K13" t="n">
         <v>10.9021</v>
@@ -1468,13 +1468,13 @@
         <v>22.8929</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4695</v>
+        <v>2.7958</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6007</v>
+        <v>3.927</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1314</v>
+        <v>-1.1315</v>
       </c>
       <c r="V13" t="n">
         <v>3.750499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.7325</v>
+        <v>7.1951</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2278</v>
+        <v>4.7276</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5047</v>
+        <v>2.4675</v>
       </c>
       <c r="G14" t="n">
         <v>2.4214</v>
@@ -1546,13 +1546,13 @@
         <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2821</v>
+        <v>0.7447</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2298</v>
+        <v>0.7297</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0523</v>
+        <v>0.0151</v>
       </c>
       <c r="V14" t="n">
         <v>2.5721</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3527</v>
+        <v>4.4201</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6052</v>
+        <v>5.5337</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2525</v>
+        <v>-1.1136</v>
       </c>
       <c r="G15" t="n">
         <v>0.9366</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5547</v>
+        <v>0.6221</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6336</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0789</v>
+        <v>0.0601</v>
       </c>
       <c r="V15" t="n">
         <v>1.4046</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9376</v>
+        <v>3.8401</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5183</v>
+        <v>1.3755</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4194</v>
+        <v>2.4645</v>
       </c>
       <c r="G16" t="n">
         <v>3.6874</v>
@@ -1702,13 +1702,13 @@
         <v>3.1218</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.4655</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9415</v>
+        <v>-0.0842</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.524</v>
+        <v>-0.4788</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1168</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4619</v>
+        <v>1.0715</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2663</v>
+        <v>0.3766</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7282</v>
+        <v>0.6949</v>
       </c>
       <c r="G17" t="n">
         <v>3.0817</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9747</v>
+        <v>-0.365</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7581</v>
+        <v>-0.1152</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2165</v>
+        <v>-0.2498</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6452</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1973</v>
+        <v>0.2854</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3063</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5036</v>
+        <v>0.5917</v>
       </c>
       <c r="G18" t="n">
         <v>0.4772</v>
@@ -1858,13 +1858,13 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2799</v>
+        <v>-0.1918</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0842</v>
+        <v>0.0039</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2305</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9389999999999999</v>
+        <v>2.0077</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7086</v>
+        <v>-2.0947</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8057</v>
+        <v>-0.3108</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.614</v>
+        <v>-0.7696</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4198</v>
+        <v>0.4588</v>
       </c>
       <c r="J19" t="n">
-        <v>0.912</v>
+        <v>1.3018</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2067</v>
+        <v>0.0959</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7054</v>
+        <v>1.2058</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1063</v>
+        <v>-1.6126</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8207</v>
+        <v>-0.8655</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7144</v>
+        <v>-0.747</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.0406</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3582</v>
+        <v>-0.0132</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5839</v>
+        <v>-0.0047</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2257</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3538</v>
+        <v>0.237</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3538</v>
+        <v>1.7513</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.379</v>
+        <v>-0.2726</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6863</v>
+        <v>-1.1534</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0653</v>
+        <v>0.8808</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3108</v>
+        <v>0.8057</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7696</v>
+        <v>-0.614</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4588</v>
+        <v>1.4198</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3018</v>
+        <v>0.912</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0959</v>
+        <v>0.2067</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2058</v>
+        <v>0.7054</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6126</v>
+        <v>-0.1063</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8655</v>
+        <v>-0.8207</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.747</v>
+        <v>0.7144</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3053</v>
+        <v>0.3161</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3262</v>
+        <v>0.3696</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>-0.0535</v>
       </c>
       <c r="V20" t="n">
-        <v>0.237</v>
+        <v>-0.3538</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7513</v>
+        <v>-0.3538</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1878</v>
+        <v>-1.5822</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0022</v>
+        <v>-1.9814</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1856</v>
+        <v>0.3992</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5608</v>
+        <v>-0.3255</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4328</v>
+        <v>-1.8955</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9936</v>
+        <v>1.57</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2968</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>1.972</v>
+        <v>-1.1114</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6752</v>
+        <v>1.0311</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8576</v>
+        <v>-0.2453</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5392</v>
+        <v>-0.7841</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3184</v>
+        <v>0.5389</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1218</v>
+        <v>0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1624</v>
+        <v>-2.2893</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>2.7055</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6811</v>
+        <v>-0.0349</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0497</v>
+        <v>0.1582</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3686</v>
+        <v>-0.193</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8137</v>
+        <v>-1.6381</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8137</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.868</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5403</v>
+        <v>-2.6585</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6244</v>
+        <v>-1.6451</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08409999999999999</v>
+        <v>-1.0134</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3255</v>
+        <v>-0.5608</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8955</v>
+        <v>0.4328</v>
       </c>
       <c r="I22" t="n">
-        <v>1.57</v>
+        <v>-0.9936</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.08019999999999999</v>
+        <v>1.2968</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1114</v>
+        <v>1.972</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0311</v>
+        <v>-0.6752</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2453</v>
+        <v>-1.8576</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7841</v>
+        <v>-1.5392</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5389</v>
+        <v>-0.3184</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4162</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2893</v>
+        <v>-4.1624</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7055</v>
+        <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9929</v>
+        <v>0.2104</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4848</v>
+        <v>0.4067</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5082</v>
+        <v>-0.1964</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6381</v>
+        <v>0.8137</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>0.8137</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4854</v>
+        <v>-2.9917</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6156</v>
+        <v>-1.2941</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8699</v>
+        <v>-1.6976</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5921</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9558</v>
+        <v>-0.4621</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.2657</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3686</v>
+        <v>-0.1964</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5213</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6308</v>
+        <v>-4.0133</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2676</v>
+        <v>-3.0533</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3632</v>
+        <v>-0.96</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3395</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3538</v>
+        <v>-0.7363</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7177</v>
+        <v>-0.5034</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6361</v>
+        <v>-0.2329</v>
       </c>
       <c r="V24" t="n">
         <v>0.23</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.0595</v>
+        <v>-9.895200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.748799999999999</v>
+        <v>-8.3202</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3107</v>
+        <v>-1.575</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7308</v>
@@ -2404,13 +2404,13 @@
         <v>1.8731</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0176</v>
+        <v>0.1468</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3543</v>
+        <v>0.0743</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3367</v>
+        <v>0.0725</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7325</v>
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.8313</v>
+        <v>-4.688199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.732599999999998</v>
+        <v>-3.732700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.0986</v>
+        <v>-0.9556999999999995</v>
       </c>
       <c r="G26" t="n">
-        <v>3.550500000000001</v>
+        <v>3.550499999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.388999999999999</v>
+        <v>-3.389</v>
       </c>
       <c r="I26" t="n">
-        <v>6.939600000000002</v>
+        <v>6.9396</v>
       </c>
       <c r="J26" t="n">
         <v>9.431900000000002</v>
@@ -2482,13 +2482,13 @@
         <v>18.7307</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.4694</v>
+        <v>-0.3261999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1315</v>
+        <v>1.1316</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.600899999999999</v>
+        <v>-1.4577</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7503</v>
